--- a/FINAL.xlsx
+++ b/FINAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5173BB6-3585-44E2-AC71-45F287962762}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0968BC88-8C7D-4CAA-BB7C-FAA9F616E5F7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -282,11 +282,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="_(&quot;Rp&quot;* #,##0_);_(&quot;Rp&quot;* \(#,##0\);_(&quot;Rp&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="0000000000000"/>
-    <numFmt numFmtId="169" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(&quot;Rp&quot;* #,##0_);_(&quot;Rp&quot;* \(#,##0\);_(&quot;Rp&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="0000000000000"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -602,15 +602,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="1" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="1" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="1" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="7" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="7" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -683,10 +683,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -695,7 +695,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -710,44 +710,44 @@
     <xf numFmtId="14" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6477,18 +6477,18 @@
     </row>
     <row r="16" spans="1:34" ht="69" customHeight="1">
       <c r="A16" s="49"/>
-      <c r="B16" s="67" t="s">
+      <c r="B16" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="65"/>
-      <c r="D16" s="65"/>
-      <c r="E16" s="65"/>
-      <c r="F16" s="65"/>
-      <c r="G16" s="65"/>
-      <c r="H16" s="65"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="65"/>
-      <c r="K16" s="66"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="66"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="66"/>
+      <c r="G16" s="66"/>
+      <c r="H16" s="66"/>
+      <c r="I16" s="66"/>
+      <c r="J16" s="66"/>
+      <c r="K16" s="67"/>
       <c r="L16" s="50">
         <f t="shared" ref="L16:Z16" si="4">SUM(L8:L15)</f>
         <v>165572750</v>
@@ -6931,7 +6931,7 @@
       <c r="AG26" s="56"/>
       <c r="AH26" s="56"/>
     </row>
-    <row r="27" spans="1:34" ht="14.25" customHeight="1">
+    <row r="27" spans="1:34" ht="33.75" customHeight="1">
       <c r="A27" s="56"/>
       <c r="B27" s="56"/>
       <c r="C27" s="57"/>
@@ -6975,7 +6975,7 @@
       <c r="AG27" s="56"/>
       <c r="AH27" s="58"/>
     </row>
-    <row r="28" spans="1:34" ht="14.25" customHeight="1">
+    <row r="28" spans="1:34" ht="36" customHeight="1">
       <c r="A28" s="56"/>
       <c r="B28" s="56"/>
       <c r="C28" s="57"/>
